--- a/stories/arbres/ATOM-VIV.ANI.003-01.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Inès rentre à la maison avec papa. Minou le chat miaule. Sa gamelle est vide. Inès veut aider. Papa dit : on le fait ensemble. On est doux. Papa verse l'eau. Inès tient le bol avec papa. L'eau arrive tout doucement. Papa met des croquettes. Inès pose la gamelle. Elle est douce. Sa main va lentement. Minou vient. Il boit. Il mange. Papa dit : on prend soin avec un adulte. On reste doux.</t>
+          <t>Inès rentre à la maison avec papa. Minou le chat miaule. Sa gamelle est vide. Inès veut aider. On le fait ensemble. On est doux. Papa verse l'eau. Inès tient le bol avec papa. L'eau arrive tout doucement. Papa met des croquettes. Inès pose la gamelle. Elle est douce. Sa main va lentement. Minou vient. Il boit. Il mange. On prend soin avec un adulte. On reste doux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rentre à la maison avec papa. Minou le chat miaule. Sa gamelle est vide. Inès veut aider.
+papa|On le fait ensemble. On est doux. Papa verse l'eau.
+narrateur|Inès tient le bol avec papa. L'eau arrive tout doucement. Papa met des croquettes. Inès pose la gamelle. Elle est douce. Sa main va lentement. Minou vient. Il boit. Il mange.
+papa|On prend soin avec un adulte. On reste doux.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Inès donne l'eau au chat. Comment fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a été douce. Elle a versé l'eau avec un adulte. Papa était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1825,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Minou ronronne. Inès s'assoit près de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1992,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2032,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.003-01.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 papa|On prend soin avec un adulte. On reste doux.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1502,7 @@
           <t>narrateur|Inès donne l'eau au chat. Comment fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1674,7 @@
           <t>narrateur|Inès a été douce. Elle a versé l'eau avec un adulte. Papa était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1830,6 +1838,7 @@
           <t>narrateur|Minou ronronne. Inès s'assoit près de papa.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1997,6 +2006,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2015,7 +2025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2039,6 +2049,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2240,6 +2264,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.ANI.003-01.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L'eau de Minou avec papa</t>
+          <t>La gamelle trop pleine</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah veut que Minou boive. La gamelle est vide. Ils versent trop. L'eau déborde. Ils essuient. Minou lape.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Inès rentre à la maison avec papa. Minou le chat miaule. Sa gamelle est vide. Inès veut aider. On le fait ensemble. On est doux. Papa verse l'eau. Inès tient le bol avec papa. L'eau arrive tout doucement. Papa met des croquettes. Inès pose la gamelle. Elle est douce. Sa main va lentement. Minou vient. Il boit. Il mange. On prend soin avec un adulte. On reste doux.</t>
+          <t>Le carrelage de la cuisine est tiède. Un carré de soleil pose une nappe jaune. Ça sent le pain d'hier, un peu. Une miette brille près du buffet. Tes pieds sont chauds, Sarah. Le sol est doux. Un miaulement arrive du couloir. Minou le chat vient. Ses pattes tapent le bois. Toc, toc, tout léger. En ce moment, Sarah regarde la gamelle. La gamelle de Minou est vide. Le fond est sec, un peu blanc. Il a soif, papa. Je veux qu'il boive. On le fait ensemble. Avec un adulte. On est doux. Tu tiens le bol avec moi ? Oui. Sarah pose les deux mains sur le bol. Le bol est froid. Papa ouvre le robinet. L'eau chante, mince. Doucement. Un peu seulement. Sarah penche le bol trop vite. L'eau monte, monte. Elle déborde. Une flaque glisse sur le carrelage. Oh. C'est trop. On arrête. On essuie. Papa prend le linge de la chaise. Le linge sent le savon. Sarah appuie avec lui. La flaque part, tout doux. Le bol, on le vide un peu ? Un peu. Ils versent l'eau en trop dans l'évier. Ça fait ploc. Il reste une lame d'eau, claire. Maintenant, on pose. Tout doux. Sarah pose la gamelle. Sa main va lentement. Le bol touche le carrelage sans bruit. Minou s'approche. Ses moustaches tremblent. Il vient. On recule un peu. On reste près de moi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Inès rentre à la maison &lt;emphasis level="moderate"&gt;avec&lt;/emphasis&gt; papa. Minou le chat miaule. Sa gamelle est vide. Inès veut aider. Papa dit : on le fait ensemble. On est doux. Papa verse l'eau. Inès tient le bol avec papa. L'eau arrive tout doucement. Papa met des croquettes. Inès pose la gamelle. Elle est douce. Sa main va lentement. Minou vient. Il boit. Il mange. Papa dit : on prend soin avec un adulte. On reste doux.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le carrelage de la cuisine est tiède. Un carré de soleil pose une nappe jaune. Ça sent le pain d'hier, un peu. Une miette brille près du buffet. Tes pieds sont chauds, Sarah. Le sol est doux. Un miaulement arrive du couloir. Minou le chat vient. Ses pattes tapent le bois. Toc, toc, tout léger. En ce moment, Sarah regarde la gamelle. La gamelle de Minou est vide. Le fond est sec, un peu blanc. Il a soif, papa. Je veux qu'il boive. On le fait ensemble. Avec un adulte. On est doux. Tu tiens le bol avec moi ? Oui. Sarah pose les deux mains sur le bol. Le bol est froid. Papa ouvre le robinet. L'eau chante, mince. Doucement. Un peu seulement. Sarah penche le bol trop vite. L'eau monte, monte. Elle déborde. Une flaque glisse sur le carrelage. Oh. C'est trop. On arrête. On essuie. Papa prend le linge de la chaise. Le linge sent le savon. Sarah appuie avec lui. La flaque part, tout doux. Le bol, on le vide un peu ? Un peu. Ils versent l'eau en trop dans l'évier. Ça fait ploc. Il reste une lame d'eau, claire. Maintenant, on pose. Tout doux. Sarah pose la gamelle. Sa main va lentement. Le bol touche le carrelage sans bruit. Minou s'approche. Ses moustaches tremblent. Il vient. On recule un peu. On reste près de moi.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,13 +1324,61 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Inès rentre à la maison avec papa. Minou le chat miaule. Sa gamelle est vide. Inès veut aider.
-papa|On le fait ensemble. On est doux. Papa verse l'eau.
-narrateur|Inès tient le bol avec papa. L'eau arrive tout doucement. Papa met des croquettes. Inès pose la gamelle. Elle est douce. Sa main va lentement. Minou vient. Il boit. Il mange.
-papa|On prend soin avec un adulte. On reste doux.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le carrelage de la cuisine est tiède.
+narrateur|Un carré de soleil pose une nappe jaune.
+narrateur|Ça sent le pain d'hier, un peu.
+narrateur|Une miette brille près du buffet.
+papa|Tes pieds sont chauds, Sarah.
+enfant-f|Le sol est doux.
+narrateur|Un miaulement arrive du couloir.
+narrateur|Minou le chat vient.
+narrateur|Ses pattes tapent le bois.
+narrateur|Toc, toc, tout léger.
+narrateur|En ce moment, Sarah regarde la gamelle.
+narrateur|La gamelle de Minou est vide.
+narrateur|Le fond est sec, un peu blanc.
+enfant-f|Il a soif, papa.
+enfant-f|Je veux qu'il boive.
+papa|On le fait ensemble.
+papa|Avec un adulte.
+papa|On est doux.
+papa|Tu tiens le bol avec moi ?
+enfant-f|Oui.
+narrateur|Sarah pose les deux mains sur le bol.
+narrateur|Le bol est froid.
+narrateur|Papa ouvre le robinet.
+narrateur|L'eau chante, mince.
+enfant-f|Doucement.
+papa|Un peu seulement.
+narrateur|Sarah penche le bol trop vite.
+narrateur|L'eau monte, monte.
+narrateur|Elle déborde.
+narrateur|Une flaque glisse sur le carrelage.
+enfant-f|Oh.
+enfant-f|C'est trop.
+papa|On arrête.
+papa|On essuie.
+narrateur|Papa prend le linge de la chaise.
+narrateur|Le linge sent le savon.
+narrateur|Sarah appuie avec lui.
+narrateur|La flaque part, tout doux.
+papa|Le bol, on le vide un peu ?
+enfant-f|Un peu.
+narrateur|Ils versent l'eau en trop dans l'évier.
+narrateur|Ça fait ploc.
+narrateur|Il reste une lame d'eau, claire.
+papa|Maintenant, on pose.
+papa|Tout doux.
+narrateur|Sarah pose la gamelle.
+narrateur|Sa main va lentement.
+narrateur|Le bol touche le carrelage sans bruit.
+narrateur|Minou s'approche.
+narrateur|Ses moustaches tremblent.
+enfant-f|Il vient.
+papa|On recule un peu.
+papa|On reste près de moi.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,12 +1403,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Inès donne l'eau au chat. Comment fait-elle ?</t>
+          <t>Sarah donne l'eau au chat. Comment fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Inès donne l'eau au chat. Comment fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah donne l'eau au chat. Comment fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1378,7 +1438,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle est douce, avec papa. Comment fait Inès ?</t>
+          <t>Elle est douce, avec papa. Comment fait Sarah ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1427,7 +1487,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1499,10 +1559,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Inès donne l'eau au chat. Comment fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Sarah donne l'eau au chat.
+narrateur|Comment fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1527,12 +1587,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Inès a été douce. Elle a versé l'eau avec un adulte. Papa était là.</t>
+          <t>Minou pose la langue. Lape, lape, lape. L'eau baisse, tout doux. Il boit. Oui. Tu as été douce. Avec un adulte. Merci, Sarah. Sarah reste assise près de papa. Elle ne prend pas Minou. Ses mains sont sur ses genoux. La flaque est partie. Oui. On a essuyé ensemble. Tu as vu le trop d'eau ? Ça déborde. Alors on verse peu. Minou lève la tête. Une goutte brille sur sa moustache. Il se lèche la patte. Il est content. Il a bu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Inès a été douce. Elle a versé l'eau &lt;emphasis level="moderate"&gt;avec&lt;/emphasis&gt; un adulte. Papa était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Minou pose la langue. Lape, lape, lape. L'eau baisse, tout doux. Il boit. Oui. Tu as été douce. Avec un adulte. Merci, Sarah. Sarah reste assise près de papa. Elle ne prend pas Minou. Ses mains sont sur ses genoux. La flaque est partie. Oui. On a essuyé ensemble. Tu as vu le trop d'eau ? Ça déborde. Alors on verse peu. Minou lève la tête. Une goutte brille sur sa moustache. Il se lèche la patte. Il est content. Il a bu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1595,7 +1655,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1671,10 +1731,30 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Inès a été douce. Elle a versé l'eau avec un adulte. Papa était là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Minou pose la langue.
+narrateur|Lape, lape, lape.
+narrateur|L'eau baisse, tout doux.
+enfant-f|Il boit.
+papa|Oui.
+papa|Tu as été douce.
+papa|Avec un adulte.
+papa|Merci, Sarah.
+narrateur|Sarah reste assise près de papa.
+narrateur|Elle ne prend pas Minou.
+narrateur|Ses mains sont sur ses genoux.
+enfant-f|La flaque est partie.
+papa|Oui.
+papa|On a essuyé ensemble.
+papa|Tu as vu le trop d'eau ?
+enfant-f|Ça déborde.
+papa|Alors on verse peu.
+narrateur|Minou lève la tête.
+narrateur|Une goutte brille sur sa moustache.
+narrateur|Il se lèche la patte.
+enfant-f|Il est content.
+papa|Il a bu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1699,12 +1779,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Minou ronronne. Inès s'assoit près de papa.</t>
+          <t>Le carré de soleil a bougé. Il touche maintenant la gamelle. L'eau restante fait un petit miroir. Je vois Minou dedans. Un Minou tout petit. Minou s'allonge près du buffet. Son ventre va, vient. Un ronron commence, bas. Tu entends ? Oui. Sarah pose l'oreille vers le sol. Le ronron est chaud. On range le linge. Sarah donne le linge à papa. Le carrelage est sec. Il a bu, papa. C'était ça, ton envie.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Minou ronronne. Inès s'assoit près de papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le carré de soleil a bougé. Il touche maintenant la gamelle. L'eau restante fait un petit miroir. Je vois Minou dedans. Un Minou tout petit. Minou s'allonge près du buffet. Son ventre va, vient. Un ronron commence, bas. Tu entends ? Oui. Sarah pose l'oreille vers le sol. Le ronron est chaud. On range le linge. Sarah donne le linge à papa. Le carrelage est sec. Il a bu, papa. C'était ça, ton envie.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1767,7 +1847,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1835,10 +1915,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Minou ronronne. Inès s'assoit près de papa.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le carré de soleil a bougé.
+narrateur|Il touche maintenant la gamelle.
+narrateur|L'eau restante fait un petit miroir.
+enfant-f|Je vois Minou dedans.
+papa|Un Minou tout petit.
+narrateur|Minou s'allonge près du buffet.
+narrateur|Son ventre va, vient.
+narrateur|Un ronron commence, bas.
+papa|Tu entends ?
+enfant-f|Oui.
+narrateur|Sarah pose l'oreille vers le sol.
+narrateur|Le ronron est chaud.
+papa|On range le linge.
+narrateur|Sarah donne le linge à papa.
+narrateur|Le carrelage est sec.
+enfant-f|Il a bu, papa.
+papa|C'était ça, ton envie.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1863,12 +1958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Minou a de l'eau. Un peu, tout doux. Une miette reste près du buffet. Le soleil la laisse d'or. La cuisine redevient calme.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Minou a de l'eau. Un peu, tout doux. Une miette reste près du buffet. Le soleil la laisse d'or. La cuisine redevient calme.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1924,14 +2019,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2003,10 +2098,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|Minou a de l'eau.
+papa|Un peu, tout doux.
+narrateur|Une miette reste près du buffet.
+narrateur|Le soleil la laisse d'or.
+narrateur|La cuisine redevient calme.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2025,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2063,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.003-01.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maison</t>
+          <t>cuisine au soleil, carrelage tiède</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Inès, papa</t>
+          <t>Sarah, papa</t>
         </is>
       </c>
     </row>
